--- a/VerveStacks_FRA_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFAB1E3E-8CDC-4FE5-B0DC-6E1DC29D295A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{015E9F3E-E68D-467D-8DAF-71EE0C8C3CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1617,7 +1617,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1753469-1850-49CE-80B8-569802886582}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3510A3F-5E14-4FE1-8B02-98F5CF395FC8}">
   <dimension ref="B2:AI108"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{015E9F3E-E68D-467D-8DAF-71EE0C8C3CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{226E2447-4BD4-4BF7-9385-2B1CBD041931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1617,7 +1617,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3510A3F-5E14-4FE1-8B02-98F5CF395FC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6BC7BD-8269-45EA-BA1D-0B76F0415B5E}">
   <dimension ref="B2:AI108"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{226E2447-4BD4-4BF7-9385-2B1CBD041931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD5856AC-2939-44D2-A4ED-31213ED2FD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1617,7 +1617,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6BC7BD-8269-45EA-BA1D-0B76F0415B5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EA683E-8B10-401F-88B1-0C08FE6733B3}">
   <dimension ref="B2:AI108"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD5856AC-2939-44D2-A4ED-31213ED2FD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED869D69-E3F2-43CF-A098-A86625A25DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -1617,7 +1617,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EA683E-8B10-401F-88B1-0C08FE6733B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{586CC672-1122-42EC-82AA-8A9DA20F5B17}">
   <dimension ref="B2:AI108"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
